--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133981996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,8 +902,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133981647</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,46 +680,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133981996</v>
+        <v>136222978</v>
       </c>
       <c r="B2" t="n">
-        <v>106199</v>
+        <v>56713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221154</v>
+        <v>206046</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,12 +761,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tillsammans med årskalv</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +790,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,16 +807,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133981996</t>
+          <t>https://artportalen.se/Sighting/136222978</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133981647</v>
+        <v>133981996</v>
       </c>
       <c r="B3" t="n">
-        <v>101324</v>
+        <v>106199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,26 +824,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222782</v>
+        <v>221154</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -903,6 +921,121 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133981996</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133981647</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogsglänta Håkmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>754460</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7097948</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Lidén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Lidén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133981647</t>
         </is>
@@ -912,6 +1045,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136222978</v>
       </c>
       <c r="B2" t="n">
-        <v>56713</v>
+        <v>56714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136222978</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>56718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136222978</v>
       </c>
       <c r="B2" t="n">
-        <v>56718</v>
+        <v>56719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136222978</v>
       </c>
       <c r="B2" t="n">
-        <v>56719</v>
+        <v>56724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51971-2025 artfynd.xlsx
+++ b/artfynd/A 51971-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136222978</v>
       </c>
       <c r="B2" t="n">
-        <v>56724</v>
+        <v>56737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
